--- a/SandBox/MathsMap/MathsCollaborators.xlsx
+++ b/SandBox/MathsMap/MathsCollaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="830" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E459EDD1-3671-4A8D-956A-93156832BCE5}"/>
+  <xr:revisionPtr revIDLastSave="841" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29863FD9-6AF5-46B8-9061-0AB3940B071A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="162">
   <si>
     <t>Institution</t>
   </si>
@@ -372,13 +372,19 @@
     <t>Hagen</t>
   </si>
   <si>
-    <t>Holy Names University</t>
-  </si>
-  <si>
-    <t>Oakland</t>
+    <t>Santa Clara University</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
   </si>
   <si>
     <t>United States</t>
+  </si>
+  <si>
+    <t>Lawrence Berkeley National Laboratory</t>
+  </si>
+  <si>
+    <t>berkeley</t>
   </si>
   <si>
     <t>IIT Trichy</t>
@@ -921,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -1544,7 +1550,7 @@
         <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
         <v>101</v>
@@ -1558,7 +1564,7 @@
         <v>118</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
         <v>101</v>
@@ -1572,7 +1578,7 @@
         <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
         <v>101</v>
@@ -1580,13 +1586,13 @@
     </row>
     <row r="47" spans="1:4" ht="15">
       <c r="A47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" t="s">
         <v>122</v>
       </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
         <v>101</v>
@@ -1594,7 +1600,7 @@
     </row>
     <row r="48" spans="1:4" ht="15">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
@@ -1608,13 +1614,13 @@
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
         <v>101</v>
@@ -1628,7 +1634,7 @@
         <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s">
         <v>101</v>
@@ -1636,13 +1642,13 @@
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s">
         <v>129</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>130</v>
-      </c>
-      <c r="C51" t="s">
-        <v>114</v>
       </c>
       <c r="D51" t="s">
         <v>101</v>
@@ -1656,7 +1662,7 @@
         <v>132</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="D52" t="s">
         <v>101</v>
@@ -1670,7 +1676,7 @@
         <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
         <v>101</v>
@@ -1678,13 +1684,13 @@
     </row>
     <row r="54" spans="1:5" ht="15">
       <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
         <v>136</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>137</v>
-      </c>
-      <c r="C54" t="s">
-        <v>69</v>
       </c>
       <c r="D54" t="s">
         <v>101</v>
@@ -1698,7 +1704,7 @@
         <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
         <v>101</v>
@@ -1712,7 +1718,7 @@
         <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D56" t="s">
         <v>101</v>
@@ -1726,98 +1732,111 @@
         <v>143</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
         <v>147</v>
       </c>
-      <c r="C59" t="s">
+    </row>
+    <row r="60" spans="1:5" ht="15">
+      <c r="A60" t="s">
         <v>148</v>
       </c>
-      <c r="D59" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15">
-      <c r="A60" s="3" t="s">
+      <c r="B60" t="s">
         <v>149</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" t="s">
         <v>150</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15">
+      <c r="A61" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="1:5" ht="15">
-      <c r="A61" t="s">
+      <c r="C61" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C61" t="s">
-        <v>155</v>
-      </c>
-      <c r="D61" t="s">
-        <v>152</v>
-      </c>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" t="s">
         <v>156</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>157</v>
       </c>
-      <c r="C62" t="s">
-        <v>158</v>
-      </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
+        <v>158</v>
+      </c>
+      <c r="B63" t="s">
         <v>159</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15">
+      <c r="A64" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" t="s">
         <v>109</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>69</v>
       </c>
-      <c r="D63" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="66" ht="15"/>
+      <c r="D64" t="s">
+        <v>154</v>
+      </c>
+    </row>
     <row r="67" ht="15"/>
     <row r="68" ht="15"/>
     <row r="69" ht="15"/>
@@ -1837,7 +1856,7 @@
     <row r="83" ht="15"/>
     <row r="84" ht="15"/>
     <row r="85" ht="15"/>
-    <row r="95" ht="15"/>
+    <row r="86" ht="15"/>
     <row r="96" ht="15"/>
     <row r="97" ht="15"/>
     <row r="98" ht="15"/>
@@ -1856,11 +1875,12 @@
     <row r="111" ht="15"/>
     <row r="112" ht="15"/>
     <row r="113" ht="15"/>
-    <row r="135" ht="15"/>
+    <row r="114" ht="15"/>
+    <row r="136" ht="15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H63">
-    <sortCondition ref="D2:D63"/>
-    <sortCondition ref="A2:A63"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H64">
+    <sortCondition ref="D2:D64"/>
+    <sortCondition ref="A2:A64"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A37" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>

--- a/SandBox/MathsMap/MathsCollaborators.xlsx
+++ b/SandBox/MathsMap/MathsCollaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="841" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29863FD9-6AF5-46B8-9061-0AB3940B071A}"/>
+  <xr:revisionPtr revIDLastSave="871" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B41F2D9-970E-4BD7-9B4B-51E9528DC665}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="175">
   <si>
     <t>Institution</t>
   </si>
@@ -520,6 +520,45 @@
   </si>
   <si>
     <t>University College Dublin</t>
+  </si>
+  <si>
+    <t>Université du Quebec à Montreal</t>
+  </si>
+  <si>
+    <t>Montreal</t>
+  </si>
+  <si>
+    <t>Università di Bologna</t>
+  </si>
+  <si>
+    <t>Bologna</t>
+  </si>
+  <si>
+    <t>Institute of Mathematical Sciences Chennai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>IIT Kanpur</t>
+  </si>
+  <si>
+    <t>Kanpur</t>
+  </si>
+  <si>
+    <t>Mathematical Sciences Insitute ANU</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Politecnico di Ancona</t>
+  </si>
+  <si>
+    <t>Ancona</t>
   </si>
 </sst>
 </file>
@@ -599,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -613,6 +652,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1837,20 +1877,108 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" ht="15"/>
-    <row r="68" ht="15"/>
-    <row r="69" ht="15"/>
-    <row r="70" ht="15"/>
-    <row r="71" ht="15"/>
-    <row r="72" ht="15"/>
-    <row r="73" ht="15"/>
-    <row r="74" ht="15"/>
-    <row r="75" ht="15"/>
-    <row r="76" ht="15"/>
-    <row r="77" ht="15"/>
-    <row r="78" ht="15"/>
-    <row r="79" ht="15"/>
-    <row r="80" ht="15"/>
+    <row r="65" spans="1:4" ht="15">
+      <c r="A65" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15">
+      <c r="A66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15">
+      <c r="A67" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15">
+      <c r="A68" t="s">
+        <v>168</v>
+      </c>
+      <c r="B68" t="s">
+        <v>169</v>
+      </c>
+      <c r="C68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15">
+      <c r="A69" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" t="s">
+        <v>172</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15">
+      <c r="A70" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15">
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" ht="15">
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" ht="15">
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" ht="15">
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" ht="15"/>
+    <row r="76" spans="1:4" ht="15"/>
+    <row r="77" spans="1:4" ht="15"/>
+    <row r="78" spans="1:4" ht="15"/>
+    <row r="79" spans="1:4" ht="15"/>
+    <row r="80" spans="1:4" ht="15"/>
     <row r="81" ht="15"/>
     <row r="82" ht="15"/>
     <row r="83" ht="15"/>

--- a/SandBox/MathsMap/MathsCollaborators.xlsx
+++ b/SandBox/MathsMap/MathsCollaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="871" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B41F2D9-970E-4BD7-9B4B-51E9528DC665}"/>
+  <xr:revisionPtr revIDLastSave="915" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A89545-C5F1-4A11-9AC1-FFCFC586CB75}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="197">
   <si>
     <t>Institution</t>
   </si>
@@ -559,6 +559,72 @@
   </si>
   <si>
     <t>Ancona</t>
+  </si>
+  <si>
+    <t>Colorado State University</t>
+  </si>
+  <si>
+    <t>Fort Collins</t>
+  </si>
+  <si>
+    <t>Joshua Maglione</t>
+  </si>
+  <si>
+    <t>Bucknell University</t>
+  </si>
+  <si>
+    <t>Lewisburg, PA</t>
+  </si>
+  <si>
+    <t>University of Trento</t>
+  </si>
+  <si>
+    <t>Trento</t>
+  </si>
+  <si>
+    <t>Kent State University</t>
+  </si>
+  <si>
+    <t>Kent, OH</t>
+  </si>
+  <si>
+    <t>California State University, Fullerton</t>
+  </si>
+  <si>
+    <t>Fullerton, CA</t>
+  </si>
+  <si>
+    <t>University of Haifa</t>
+  </si>
+  <si>
+    <t>Haifa</t>
+  </si>
+  <si>
+    <t>University of Oregon</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>Monash University</t>
+  </si>
+  <si>
+    <t>Melbourne</t>
+  </si>
+  <si>
+    <t>Incheon National University</t>
+  </si>
+  <si>
+    <t>Incheon</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>University of Lincoln</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
   </si>
 </sst>
 </file>
@@ -638,7 +704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -652,7 +718,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1887,7 +1952,7 @@
       <c r="C65" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1901,7 +1966,7 @@
       <c r="C66" t="s">
         <v>31</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1915,7 +1980,7 @@
       <c r="C67" t="s">
         <v>105</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1929,7 +1994,7 @@
       <c r="C68" t="s">
         <v>105</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1943,7 +2008,7 @@
       <c r="C69" t="s">
         <v>172</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1957,28 +2022,150 @@
       <c r="C70" t="s">
         <v>31</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15">
-      <c r="D71" s="7"/>
+      <c r="A71" t="s">
+        <v>175</v>
+      </c>
+      <c r="B71" t="s">
+        <v>176</v>
+      </c>
+      <c r="C71" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="72" spans="1:4" ht="15">
-      <c r="D72" s="7"/>
+      <c r="A72" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" t="s">
+        <v>179</v>
+      </c>
+      <c r="C72" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="73" spans="1:4" ht="15">
-      <c r="D73" s="7"/>
+      <c r="A73" t="s">
+        <v>180</v>
+      </c>
+      <c r="B73" t="s">
+        <v>181</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="74" spans="1:4" ht="15">
-      <c r="D74" s="7"/>
-    </row>
-    <row r="75" spans="1:4" ht="15"/>
-    <row r="76" spans="1:4" ht="15"/>
-    <row r="77" spans="1:4" ht="15"/>
-    <row r="78" spans="1:4" ht="15"/>
-    <row r="79" spans="1:4" ht="15"/>
-    <row r="80" spans="1:4" ht="15"/>
+      <c r="A74" t="s">
+        <v>182</v>
+      </c>
+      <c r="B74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15">
+      <c r="A75" t="s">
+        <v>184</v>
+      </c>
+      <c r="B75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15">
+      <c r="A76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" t="s">
+        <v>187</v>
+      </c>
+      <c r="C76" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15">
+      <c r="A77" t="s">
+        <v>188</v>
+      </c>
+      <c r="B77" t="s">
+        <v>189</v>
+      </c>
+      <c r="C77" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15">
+      <c r="A78" t="s">
+        <v>190</v>
+      </c>
+      <c r="B78" t="s">
+        <v>191</v>
+      </c>
+      <c r="C78" t="s">
+        <v>172</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15">
+      <c r="A79" t="s">
+        <v>192</v>
+      </c>
+      <c r="B79" t="s">
+        <v>193</v>
+      </c>
+      <c r="C79" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15">
+      <c r="A80" t="s">
+        <v>195</v>
+      </c>
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
     <row r="81" ht="15"/>
     <row r="82" ht="15"/>
     <row r="83" ht="15"/>

--- a/SandBox/MathsMap/MathsCollaborators.xlsx
+++ b/SandBox/MathsMap/MathsCollaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="915" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A89545-C5F1-4A11-9AC1-FFCFC586CB75}"/>
+  <xr:revisionPtr revIDLastSave="968" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753479BA-D8F8-42E6-838B-F70F67E27FF4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="211">
   <si>
     <t>Institution</t>
   </si>
@@ -123,13 +123,49 @@
     <t>Chicago</t>
   </si>
   <si>
+    <t>IIT Kanpur</t>
+  </si>
+  <si>
+    <t>Kanpur</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Institute of Mathematical Sciences Chennai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Mathematical Sciences Insitute ANU</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Politecnico di Ancona</t>
+  </si>
+  <si>
+    <t>Ancona</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
     <t>Politecnico di Milano</t>
   </si>
   <si>
     <t>Milano</t>
   </si>
   <si>
-    <t>Italy</t>
+    <t>Università di Bologna</t>
+  </si>
+  <si>
+    <t>Bologna</t>
   </si>
   <si>
     <t>Università di Roma Tor Vergata</t>
@@ -138,6 +174,12 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>Université du Quebec à Montreal</t>
+  </si>
+  <si>
+    <t>Montreal</t>
+  </si>
+  <si>
     <t>University of Notre Dame</t>
   </si>
   <si>
@@ -228,15 +270,21 @@
     <t>Belgium</t>
   </si>
   <si>
+    <t>Bristol University</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Lancaster University</t>
   </si>
   <si>
     <t>Lancaster</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
     <t>Mary Immaculate College</t>
   </si>
   <si>
@@ -285,6 +333,72 @@
     <t>Japan</t>
   </si>
   <si>
+    <t>Bucknell University</t>
+  </si>
+  <si>
+    <t>Lewisburg, PA</t>
+  </si>
+  <si>
+    <t>Joshua Maglione</t>
+  </si>
+  <si>
+    <t>California State University, Fullerton</t>
+  </si>
+  <si>
+    <t>Fullerton, CA</t>
+  </si>
+  <si>
+    <t>Colorado State University</t>
+  </si>
+  <si>
+    <t>Fort Collins</t>
+  </si>
+  <si>
+    <t>Incheon National University</t>
+  </si>
+  <si>
+    <t>Incheon</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Kent State University</t>
+  </si>
+  <si>
+    <t>Kent, OH</t>
+  </si>
+  <si>
+    <t>Monash University</t>
+  </si>
+  <si>
+    <t>Melbourne</t>
+  </si>
+  <si>
+    <t>University of Haifa</t>
+  </si>
+  <si>
+    <t>Haifa</t>
+  </si>
+  <si>
+    <t>University of Lincoln</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>University of Oregon</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>University of Trento</t>
+  </si>
+  <si>
+    <t>Trento</t>
+  </si>
+  <si>
     <t>IITIS, Polish Academy of Sciences</t>
   </si>
   <si>
@@ -351,9 +465,6 @@
     <t>Cooch Behar</t>
   </si>
   <si>
-    <t>India</t>
-  </si>
-  <si>
     <t>DIT University</t>
   </si>
   <si>
@@ -372,42 +483,42 @@
     <t>Hagen</t>
   </si>
   <si>
+    <t>IIT Trichy</t>
+  </si>
+  <si>
+    <t>Tiruchirappalli</t>
+  </si>
+  <si>
+    <t>Lawrence Berkeley National Laboratory</t>
+  </si>
+  <si>
+    <t>Berkeley</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Maynooth University</t>
+  </si>
+  <si>
+    <t>Kildare</t>
+  </si>
+  <si>
+    <t>Memorial University of Newfoundland</t>
+  </si>
+  <si>
+    <t>St. John’s</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
     <t>Santa Clara University</t>
   </si>
   <si>
     <t>Santa Clara</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Lawrence Berkeley National Laboratory</t>
-  </si>
-  <si>
-    <t>berkeley</t>
-  </si>
-  <si>
-    <t>IIT Trichy</t>
-  </si>
-  <si>
-    <t>Tiruchirappalli</t>
-  </si>
-  <si>
-    <t>Maynooth University</t>
-  </si>
-  <si>
-    <t>Kildare</t>
-  </si>
-  <si>
-    <t>Memorial University of Newfoundland</t>
-  </si>
-  <si>
-    <t>St. John’s</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
     <t>Technical University of Dublin</t>
   </si>
   <si>
@@ -522,116 +633,47 @@
     <t>University College Dublin</t>
   </si>
   <si>
-    <t>Université du Quebec à Montreal</t>
-  </si>
-  <si>
-    <t>Montreal</t>
-  </si>
-  <si>
-    <t>Università di Bologna</t>
-  </si>
-  <si>
-    <t>Bologna</t>
-  </si>
-  <si>
-    <t>Institute of Mathematical Sciences Chennai</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>IIT Kanpur</t>
-  </si>
-  <si>
-    <t>Kanpur</t>
-  </si>
-  <si>
-    <t>Mathematical Sciences Insitute ANU</t>
-  </si>
-  <si>
-    <t>Canberra</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Politecnico di Ancona</t>
-  </si>
-  <si>
-    <t>Ancona</t>
-  </si>
-  <si>
-    <t>Colorado State University</t>
-  </si>
-  <si>
-    <t>Fort Collins</t>
-  </si>
-  <si>
-    <t>Joshua Maglione</t>
-  </si>
-  <si>
-    <t>Bucknell University</t>
-  </si>
-  <si>
-    <t>Lewisburg, PA</t>
-  </si>
-  <si>
-    <t>University of Trento</t>
-  </si>
-  <si>
-    <t>Trento</t>
-  </si>
-  <si>
-    <t>Kent State University</t>
-  </si>
-  <si>
-    <t>Kent, OH</t>
-  </si>
-  <si>
-    <t>California State University, Fullerton</t>
-  </si>
-  <si>
-    <t>Fullerton, CA</t>
-  </si>
-  <si>
-    <t>University of Haifa</t>
-  </si>
-  <si>
-    <t>Haifa</t>
-  </si>
-  <si>
-    <t>University of Oregon</t>
-  </si>
-  <si>
-    <t>Eugene, OR</t>
-  </si>
-  <si>
-    <t>Monash University</t>
-  </si>
-  <si>
-    <t>Melbourne</t>
-  </si>
-  <si>
-    <t>Incheon National University</t>
-  </si>
-  <si>
-    <t>Incheon</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>University of Lincoln</t>
-  </si>
-  <si>
-    <t>Lincoln</t>
+    <t>Dane Flannery</t>
+  </si>
+  <si>
+    <t>Universidad de Sevilla</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>University of Huddersfield</t>
+  </si>
+  <si>
+    <t>Huddersfield</t>
+  </si>
+  <si>
+    <t>Nina Snigireva</t>
+  </si>
+  <si>
+    <t>Nicolaus Copernicus University in Torun</t>
+  </si>
+  <si>
+    <t>Torun</t>
+  </si>
+  <si>
+    <t>Lodz University of Technology</t>
+  </si>
+  <si>
+    <t>Lodz</t>
+  </si>
+  <si>
+    <t>University of Florida</t>
+  </si>
+  <si>
+    <t>Florida</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -667,6 +709,12 @@
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -704,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -718,6 +766,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1032,13 +1081,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1207,7 +1256,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -1215,72 +1264,72 @@
     </row>
     <row r="13" spans="1:8" ht="15">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>38</v>
+      <c r="D14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15">
@@ -1293,8 +1342,8 @@
       <c r="C18" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>38</v>
+      <c r="D18" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15">
@@ -1305,273 +1354,273 @@
         <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15">
       <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="21" spans="1:4" ht="15">
-      <c r="A21" s="6" t="s">
-        <v>54</v>
+      <c r="A21" t="s">
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
+        <v>26</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15">
       <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
       <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
+        <v>26</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15">
       <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>57</v>
+      <c r="D23" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" t="s">
-        <v>57</v>
+        <v>6</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" t="s">
-        <v>57</v>
+        <v>16</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15">
       <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
         <v>70</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D27" t="s">
         <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15">
       <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
         <v>80</v>
       </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>82</v>
-      </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
         <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
         <v>101</v>
@@ -1579,27 +1628,27 @@
     </row>
     <row r="39" spans="1:4" ht="15">
       <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
         <v>103</v>
       </c>
-      <c r="B39" t="s">
-        <v>104</v>
-      </c>
       <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
         <v>101</v>
@@ -1607,27 +1656,27 @@
     </row>
     <row r="41" spans="1:4" ht="15">
       <c r="A41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" t="s">
         <v>108</v>
       </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D41" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15">
       <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
         <v>110</v>
       </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
         <v>101</v>
@@ -1635,69 +1684,69 @@
     </row>
     <row r="43" spans="1:4" ht="15">
       <c r="A43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s">
         <v>112</v>
       </c>
-      <c r="B43" t="s">
-        <v>113</v>
-      </c>
       <c r="C43" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
         <v>101</v>
@@ -1705,440 +1754,440 @@
     </row>
     <row r="48" spans="1:4" ht="15">
       <c r="A48" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" t="s">
         <v>124</v>
       </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="15">
+    </row>
+    <row r="49" spans="1:4" ht="15">
       <c r="A49" t="s">
         <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15">
+      <c r="A52" t="s">
+        <v>133</v>
+      </c>
+      <c r="B52" t="s">
+        <v>134</v>
+      </c>
+      <c r="C52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15">
+      <c r="A53" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15">
+      <c r="A54" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" t="s">
         <v>127</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15">
+      <c r="A55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15">
+      <c r="A56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15">
+      <c r="A57" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15">
+      <c r="A59" t="s">
+        <v>147</v>
+      </c>
+      <c r="B59" t="s">
+        <v>148</v>
+      </c>
+      <c r="C59" t="s">
         <v>26</v>
       </c>
-      <c r="D50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15">
-      <c r="A51" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" t="s">
-        <v>129</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="D59" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15">
+      <c r="A61" t="s">
+        <v>151</v>
+      </c>
+      <c r="B61" t="s">
+        <v>152</v>
+      </c>
+      <c r="C61" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15">
+      <c r="A62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" t="s">
+        <v>85</v>
+      </c>
+      <c r="D62" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15">
+      <c r="A63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D63" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15">
+      <c r="A64" t="s">
+        <v>159</v>
+      </c>
+      <c r="B64" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" t="s">
+        <v>153</v>
+      </c>
+      <c r="D64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15">
+      <c r="A65" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15">
+      <c r="A66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15">
+      <c r="A67" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15">
+      <c r="A68" t="s">
+        <v>165</v>
+      </c>
+      <c r="B68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C68" t="s">
+        <v>167</v>
+      </c>
+      <c r="D68" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15">
+      <c r="A69" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" t="s">
+        <v>169</v>
+      </c>
+      <c r="C69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15">
+      <c r="A70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15">
+      <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15">
+      <c r="A72" t="s">
+        <v>175</v>
+      </c>
+      <c r="B72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15">
+      <c r="A73" t="s">
+        <v>177</v>
+      </c>
+      <c r="B73" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15">
+      <c r="A74" t="s">
+        <v>179</v>
+      </c>
+      <c r="B74" t="s">
+        <v>180</v>
+      </c>
+      <c r="C74" t="s">
         <v>130</v>
       </c>
-      <c r="D51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15">
-      <c r="A52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" t="s">
-        <v>132</v>
-      </c>
-      <c r="C52" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15">
-      <c r="A53" t="s">
-        <v>133</v>
-      </c>
-      <c r="B53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C53" t="s">
-        <v>69</v>
-      </c>
-      <c r="D53" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15">
-      <c r="A54" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15">
-      <c r="A55" t="s">
-        <v>138</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="D74" t="s">
         <v>139</v>
       </c>
-      <c r="C55" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="15">
-      <c r="A56" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="15">
-      <c r="A57" t="s">
-        <v>142</v>
-      </c>
-      <c r="B57" t="s">
-        <v>143</v>
-      </c>
-      <c r="C57" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15">
-      <c r="A58" t="s">
-        <v>144</v>
-      </c>
-      <c r="B58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C58" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15">
-      <c r="A59" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" t="s">
+    </row>
+    <row r="75" spans="1:5" ht="15">
+      <c r="A75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" t="s">
+        <v>182</v>
+      </c>
+      <c r="C75" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15">
+      <c r="A76" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" t="s">
+        <v>95</v>
+      </c>
+      <c r="C76" t="s">
         <v>19</v>
       </c>
-      <c r="D59" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15">
-      <c r="A60" t="s">
-        <v>148</v>
-      </c>
-      <c r="B60" t="s">
-        <v>149</v>
-      </c>
-      <c r="C60" t="s">
-        <v>150</v>
-      </c>
-      <c r="D60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15">
-      <c r="A61" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E61" s="4"/>
-    </row>
-    <row r="62" spans="1:5" ht="15">
-      <c r="A62" t="s">
-        <v>155</v>
-      </c>
-      <c r="B62" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" t="s">
-        <v>157</v>
-      </c>
-      <c r="D62" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15">
-      <c r="A63" t="s">
-        <v>158</v>
-      </c>
-      <c r="B63" t="s">
-        <v>159</v>
-      </c>
-      <c r="C63" t="s">
-        <v>160</v>
-      </c>
-      <c r="D63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15">
-      <c r="A64" t="s">
-        <v>161</v>
-      </c>
-      <c r="B64" t="s">
-        <v>109</v>
-      </c>
-      <c r="C64" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15">
-      <c r="A65" t="s">
-        <v>162</v>
-      </c>
-      <c r="B65" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15">
-      <c r="A66" t="s">
-        <v>164</v>
-      </c>
-      <c r="B66" t="s">
-        <v>165</v>
-      </c>
-      <c r="C66" t="s">
-        <v>31</v>
-      </c>
-      <c r="D66" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15">
-      <c r="A67" t="s">
-        <v>166</v>
-      </c>
-      <c r="B67" t="s">
-        <v>167</v>
-      </c>
-      <c r="C67" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15">
-      <c r="A68" t="s">
-        <v>168</v>
-      </c>
-      <c r="B68" t="s">
-        <v>169</v>
-      </c>
-      <c r="C68" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15">
-      <c r="A69" t="s">
-        <v>170</v>
-      </c>
-      <c r="B69" t="s">
-        <v>171</v>
-      </c>
-      <c r="C69" t="s">
-        <v>172</v>
-      </c>
-      <c r="D69" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15">
-      <c r="A70" t="s">
-        <v>173</v>
-      </c>
-      <c r="B70" t="s">
-        <v>174</v>
-      </c>
-      <c r="C70" t="s">
-        <v>31</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15">
-      <c r="A71" t="s">
-        <v>175</v>
-      </c>
-      <c r="B71" t="s">
-        <v>176</v>
-      </c>
-      <c r="C71" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15">
-      <c r="A72" t="s">
-        <v>178</v>
-      </c>
-      <c r="B72" t="s">
-        <v>179</v>
-      </c>
-      <c r="C72" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15">
-      <c r="A73" t="s">
-        <v>180</v>
-      </c>
-      <c r="B73" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" t="s">
-        <v>31</v>
-      </c>
-      <c r="D73" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15">
-      <c r="A74" t="s">
-        <v>182</v>
-      </c>
-      <c r="B74" t="s">
-        <v>183</v>
-      </c>
-      <c r="C74" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15">
-      <c r="A75" t="s">
+      <c r="D76" t="s">
         <v>184</v>
       </c>
-      <c r="B75" t="s">
+    </row>
+    <row r="77" spans="1:5" ht="15">
+      <c r="A77" t="s">
         <v>185</v>
       </c>
-      <c r="C75" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15">
-      <c r="A76" t="s">
+      <c r="B77" t="s">
         <v>186</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C77" t="s">
         <v>187</v>
       </c>
-      <c r="C76" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15">
-      <c r="A77" t="s">
+      <c r="D77" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15">
+      <c r="A78" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C77" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="15">
-      <c r="A78" t="s">
+      <c r="C78" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C78" t="s">
-        <v>172</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15">
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="1:5" ht="15">
       <c r="A79" t="s">
         <v>192</v>
       </c>
@@ -2148,11 +2197,11 @@
       <c r="C79" t="s">
         <v>194</v>
       </c>
-      <c r="D79" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15">
+      <c r="D79" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15">
       <c r="A80" t="s">
         <v>195</v>
       </c>
@@ -2160,19 +2209,138 @@
         <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="81" ht="15"/>
-    <row r="82" ht="15"/>
-    <row r="83" ht="15"/>
-    <row r="84" ht="15"/>
-    <row r="85" ht="15"/>
-    <row r="86" ht="15"/>
-    <row r="96" ht="15"/>
+        <v>197</v>
+      </c>
+      <c r="D80" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15">
+      <c r="A81" t="s">
+        <v>198</v>
+      </c>
+      <c r="B81" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" t="s">
+        <v>85</v>
+      </c>
+      <c r="D81" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15">
+      <c r="A82" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B82" t="s">
+        <v>105</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15">
+      <c r="A83" t="s">
+        <v>200</v>
+      </c>
+      <c r="B83" t="s">
+        <v>201</v>
+      </c>
+      <c r="C83" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15">
+      <c r="A84" t="s">
+        <v>202</v>
+      </c>
+      <c r="B84" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" t="s">
+        <v>80</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15">
+      <c r="A85" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15">
+      <c r="A86" t="s">
+        <v>198</v>
+      </c>
+      <c r="B86" t="s">
+        <v>146</v>
+      </c>
+      <c r="C86" t="s">
+        <v>85</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15">
+      <c r="A87" t="s">
+        <v>205</v>
+      </c>
+      <c r="B87" t="s">
+        <v>206</v>
+      </c>
+      <c r="C87" t="s">
+        <v>123</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>207</v>
+      </c>
+      <c r="B88" t="s">
+        <v>208</v>
+      </c>
+      <c r="C88" t="s">
+        <v>123</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>209</v>
+      </c>
+      <c r="B89" t="s">
+        <v>210</v>
+      </c>
+      <c r="C89" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
     <row r="97" ht="15"/>
     <row r="98" ht="15"/>
     <row r="99" ht="15"/>
@@ -2191,14 +2359,15 @@
     <row r="112" ht="15"/>
     <row r="113" ht="15"/>
     <row r="114" ht="15"/>
-    <row r="136" ht="15"/>
+    <row r="115" ht="15"/>
+    <row r="137" ht="15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H64">
-    <sortCondition ref="D2:D64"/>
-    <sortCondition ref="A2:A64"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H81">
+    <sortCondition ref="D2:D81"/>
+    <sortCondition ref="A2:A81"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A37" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
+    <hyperlink ref="A54" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/SandBox/MathsMap/MathsCollaborators.xlsx
+++ b/SandBox/MathsMap/MathsCollaborators.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27411"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="968" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753479BA-D8F8-42E6-838B-F70F67E27FF4}"/>
+  <xr:revisionPtr revIDLastSave="1001" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78B96149-70AF-40A5-B09E-C6151DD53EE5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="218">
   <si>
     <t>Institution</t>
   </si>
@@ -48,18 +48,279 @@
     <t>Who</t>
   </si>
   <si>
+    <t>Cardiff University</t>
+  </si>
+  <si>
+    <t>Cardiff</t>
+  </si>
+  <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>Rachel Quinlan</t>
+  </si>
+  <si>
+    <t>National Science Foundation</t>
+  </si>
+  <si>
+    <t>Alexandria</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Götz Pfeiffer</t>
+  </si>
+  <si>
+    <t>DePaul University</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Angela Carnevale</t>
+  </si>
+  <si>
+    <t>University of Oregon</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>Joshua Maglione</t>
+  </si>
+  <si>
+    <t>University of Florida</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Nina Snigireva</t>
+  </si>
+  <si>
+    <t>Colorado State University</t>
+  </si>
+  <si>
+    <t>Fort Collins</t>
+  </si>
+  <si>
+    <t>Dane Flannery</t>
+  </si>
+  <si>
+    <t>California State University, Fullerton</t>
+  </si>
+  <si>
+    <t>Fullerton, CA</t>
+  </si>
+  <si>
+    <t>Kent State University</t>
+  </si>
+  <si>
+    <t>Kent, OH</t>
+  </si>
+  <si>
+    <t>Bucknell University</t>
+  </si>
+  <si>
+    <t>Lewisburg, PA</t>
+  </si>
+  <si>
     <t>Marquette University</t>
   </si>
   <si>
     <t>Milwaukee, Wisconsin</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
     <t>Aisling McCluskey</t>
   </si>
   <si>
+    <t>University of Notre Dame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notre Dame </t>
+  </si>
+  <si>
+    <t>University of Arizona</t>
+  </si>
+  <si>
+    <t>Tucson</t>
+  </si>
+  <si>
+    <t>Lawrence Berkeley National Laboratory</t>
+  </si>
+  <si>
+    <t>Berkeley</t>
+  </si>
+  <si>
+    <t>Niall Madden</t>
+  </si>
+  <si>
+    <t>Tufts Univerity</t>
+  </si>
+  <si>
+    <t>Medford</t>
+  </si>
+  <si>
+    <t>Santa Clara University</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Bristol University</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>James Cruickshank</t>
+  </si>
+  <si>
+    <t>University of Cambridge</t>
+  </si>
+  <si>
+    <t>Cambridge</t>
+  </si>
+  <si>
+    <t>Michael Mc Gettrick</t>
+  </si>
+  <si>
+    <t>University of Huddersfield</t>
+  </si>
+  <si>
+    <t>Huddersfield</t>
+  </si>
+  <si>
+    <t>Lancaster University</t>
+  </si>
+  <si>
+    <t>Lancaster</t>
+  </si>
+  <si>
+    <t>Queen Mary University of London</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>University of Oxford</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>Zayed University</t>
+  </si>
+  <si>
+    <t>Dubai</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>University of Birmingham</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
+  </si>
+  <si>
+    <t>University of Lincoln</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>University of St Andrews</t>
+  </si>
+  <si>
+    <t>St Andrews</t>
+  </si>
+  <si>
+    <t>University of Wolverhampton</t>
+  </si>
+  <si>
+    <t>Wolverhampton</t>
+  </si>
+  <si>
+    <t>Kastamonu University</t>
+  </si>
+  <si>
+    <t>Kastamonu</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Universidad de Sevilla</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Universidad Rovira i Verguli</t>
+  </si>
+  <si>
+    <t>Tarragona</t>
+  </si>
+  <si>
+    <t>University of Zaragoza</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Incheon National University</t>
+  </si>
+  <si>
+    <t>Incheon</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>University of Gdansk</t>
+  </si>
+  <si>
+    <t>Gdansk</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>IITIS, Polish Academy of Sciences</t>
+  </si>
+  <si>
+    <t>Gliwice</t>
+  </si>
+  <si>
+    <t>Lodz University of Technology</t>
+  </si>
+  <si>
+    <t>Lodz</t>
+  </si>
+  <si>
+    <t>Nicolaus Copernicus University in Torun</t>
+  </si>
+  <si>
+    <t>Torun</t>
+  </si>
+  <si>
+    <t>University of Auckland</t>
+  </si>
+  <si>
+    <t>Auckland</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
     <t>Queen's University Belfast</t>
   </si>
   <si>
@@ -69,22 +330,256 @@
     <t>N. Ireland</t>
   </si>
   <si>
-    <t>University of Auckland</t>
-  </si>
-  <si>
-    <t>Auckland</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>University of Birmingham</t>
-  </si>
-  <si>
-    <t>Birmingham</t>
-  </si>
-  <si>
-    <t>UK</t>
+    <t>University of Tokyo</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Politecnico di Ancona</t>
+  </si>
+  <si>
+    <t>Ancona</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Università di Bologna</t>
+  </si>
+  <si>
+    <t>Bologna</t>
+  </si>
+  <si>
+    <t>Politecnico di Milano</t>
+  </si>
+  <si>
+    <t>Milano</t>
+  </si>
+  <si>
+    <t>Università di Roma Tor Vergata</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>University of Trento</t>
+  </si>
+  <si>
+    <t>Trento</t>
+  </si>
+  <si>
+    <t>Bar-Ilan University</t>
+  </si>
+  <si>
+    <t>Bar-Ilan</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>University of Haifa</t>
+  </si>
+  <si>
+    <t>Haifa</t>
+  </si>
+  <si>
+    <t>University College Cork</t>
+  </si>
+  <si>
+    <t>Cork</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>University College Dublin</t>
+  </si>
+  <si>
+    <t>Dublin</t>
+  </si>
+  <si>
+    <t>Ray Ryan</t>
+  </si>
+  <si>
+    <t>Dublin City University</t>
+  </si>
+  <si>
+    <t>Technical University of Dublin</t>
+  </si>
+  <si>
+    <t>Trinity College Dublin</t>
+  </si>
+  <si>
+    <t>Maynooth University</t>
+  </si>
+  <si>
+    <t>Kildare</t>
+  </si>
+  <si>
+    <t>University of Limerick</t>
+  </si>
+  <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>Mary Immaculate College</t>
+  </si>
+  <si>
+    <t>Thurles</t>
+  </si>
+  <si>
+    <t>Middle Technical University Baghdad</t>
+  </si>
+  <si>
+    <t>Baghdad</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Institute of Mathematical Sciences Chennai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Cooch Behar Panchanan Barma University</t>
+  </si>
+  <si>
+    <t>Cooch Behar</t>
+  </si>
+  <si>
+    <t>DIT University</t>
+  </si>
+  <si>
+    <t>Dehradun</t>
+  </si>
+  <si>
+    <t>IIT Kanpur</t>
+  </si>
+  <si>
+    <t>Kanpur</t>
+  </si>
+  <si>
+    <t>IIT Trichy</t>
+  </si>
+  <si>
+    <t>Tiruchirappalli</t>
+  </si>
+  <si>
+    <t>ELTE Eotvos Lorand University</t>
+  </si>
+  <si>
+    <t>Budapest</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>RWTH Aachen</t>
+  </si>
+  <si>
+    <t>Aachen</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Bielefeld University</t>
+  </si>
+  <si>
+    <t>Bielefeld</t>
+  </si>
+  <si>
+    <t>Ruhr-Universität Bochum</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>TU Dresden</t>
+  </si>
+  <si>
+    <t>Dresden</t>
+  </si>
+  <si>
+    <t>FernUniversitat in Hagen</t>
+  </si>
+  <si>
+    <t>Hagen</t>
+  </si>
+  <si>
+    <t>Universität Stuttgart</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Université de Picardie Jules Verne</t>
+  </si>
+  <si>
+    <t>Amiens</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Universite Grenoble Alpes</t>
+  </si>
+  <si>
+    <t>Grenoble</t>
+  </si>
+  <si>
+    <t>Abo Adakemi</t>
+  </si>
+  <si>
+    <t>Turku</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>University of Cyprus</t>
+  </si>
+  <si>
+    <t>Nicosia</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Chinese Academy of Sciences</t>
+  </si>
+  <si>
+    <t>Beijing</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Computational Science Research Center</t>
+  </si>
+  <si>
+    <t>Nanjing University of Aeronautics and Astronautics</t>
+  </si>
+  <si>
+    <t>Nanjing</t>
+  </si>
+  <si>
+    <t>Universidad Austral de Chile</t>
+  </si>
+  <si>
+    <t>Valdvia</t>
+  </si>
+  <si>
+    <t>Chile</t>
   </si>
   <si>
     <t>University of New Brunswick</t>
@@ -96,46 +591,52 @@
     <t xml:space="preserve">Canada </t>
   </si>
   <si>
-    <t>Bar-Ilan University</t>
-  </si>
-  <si>
-    <t>Bar-Ilan</t>
-  </si>
-  <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t>Angela Carnevale</t>
-  </si>
-  <si>
-    <t>Bielefeld University</t>
-  </si>
-  <si>
-    <t>Bielefeld</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>DePaul University</t>
-  </si>
-  <si>
-    <t>Chicago</t>
-  </si>
-  <si>
-    <t>IIT Kanpur</t>
-  </si>
-  <si>
-    <t>Kanpur</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Institute of Mathematical Sciences Chennai</t>
-  </si>
-  <si>
-    <t>Chennai</t>
+    <t>Université du Quebec à Montreal</t>
+  </si>
+  <si>
+    <t>Montreal</t>
+  </si>
+  <si>
+    <t>University of Regina</t>
+  </si>
+  <si>
+    <t>Regina</t>
+  </si>
+  <si>
+    <t>Memorial University of Newfoundland</t>
+  </si>
+  <si>
+    <t>St. John’s</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Universidade Federal do Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>KU Leuven</t>
+  </si>
+  <si>
+    <t>Leuven</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>TU Wien</t>
+  </si>
+  <si>
+    <t>Vienna</t>
+  </si>
+  <si>
+    <t>Austria</t>
   </si>
   <si>
     <t>Mathematical Sciences Insitute ANU</t>
@@ -147,471 +648,12 @@
     <t>Australia</t>
   </si>
   <si>
-    <t>Politecnico di Ancona</t>
-  </si>
-  <si>
-    <t>Ancona</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>Politecnico di Milano</t>
-  </si>
-  <si>
-    <t>Milano</t>
-  </si>
-  <si>
-    <t>Università di Bologna</t>
-  </si>
-  <si>
-    <t>Bologna</t>
-  </si>
-  <si>
-    <t>Università di Roma Tor Vergata</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Université du Quebec à Montreal</t>
-  </si>
-  <si>
-    <t>Montreal</t>
-  </si>
-  <si>
-    <t>University of Notre Dame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notre Dame </t>
-  </si>
-  <si>
-    <t>National Science Foundation</t>
-  </si>
-  <si>
-    <t>Alexandria</t>
-  </si>
-  <si>
-    <t>Götz Pfeiffer</t>
-  </si>
-  <si>
-    <t>Ruhr-Universität Bochum</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>RWTH Aachen</t>
-  </si>
-  <si>
-    <t>Aachen</t>
-  </si>
-  <si>
-    <t>Universität Stuttgart</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Université de Picardie Jules Verne</t>
-  </si>
-  <si>
-    <t>Amiens</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>University of Arizona</t>
-  </si>
-  <si>
-    <t>Tucson</t>
-  </si>
-  <si>
-    <t>University of St Andrews</t>
-  </si>
-  <si>
-    <t>St Andrews</t>
-  </si>
-  <si>
-    <t>University of Wolverhampton</t>
-  </si>
-  <si>
-    <t>Wolverhampton</t>
-  </si>
-  <si>
-    <t>ELTE Eotvos Lorand University</t>
-  </si>
-  <si>
-    <t>Budapest</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>James Cruickshank</t>
-  </si>
-  <si>
-    <t>Kastamonu University</t>
-  </si>
-  <si>
-    <t>Kastamonu</t>
-  </si>
-  <si>
-    <t>Turkey</t>
-  </si>
-  <si>
-    <t>KU Leuven</t>
-  </si>
-  <si>
-    <t>Leuven</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Bristol University</t>
-  </si>
-  <si>
-    <t>Bristol</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Lancaster University</t>
-  </si>
-  <si>
-    <t>Lancaster</t>
-  </si>
-  <si>
-    <t>Mary Immaculate College</t>
-  </si>
-  <si>
-    <t>Thurles</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Middle Technical University Baghdad</t>
-  </si>
-  <si>
-    <t>Baghdad</t>
-  </si>
-  <si>
-    <t>Iraq</t>
-  </si>
-  <si>
-    <t>Queen Mary University of London</t>
-  </si>
-  <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>Universidad Austral de Chile</t>
-  </si>
-  <si>
-    <t>Valdvia</t>
-  </si>
-  <si>
-    <t>Chile</t>
-  </si>
-  <si>
-    <t>University of Regina</t>
-  </si>
-  <si>
-    <t>Regina</t>
-  </si>
-  <si>
-    <t>University of Tokyo</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Bucknell University</t>
-  </si>
-  <si>
-    <t>Lewisburg, PA</t>
-  </si>
-  <si>
-    <t>Joshua Maglione</t>
-  </si>
-  <si>
-    <t>California State University, Fullerton</t>
-  </si>
-  <si>
-    <t>Fullerton, CA</t>
-  </si>
-  <si>
-    <t>Colorado State University</t>
-  </si>
-  <si>
-    <t>Fort Collins</t>
-  </si>
-  <si>
-    <t>Incheon National University</t>
-  </si>
-  <si>
-    <t>Incheon</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>Kent State University</t>
-  </si>
-  <si>
-    <t>Kent, OH</t>
-  </si>
-  <si>
     <t>Monash University</t>
   </si>
   <si>
     <t>Melbourne</t>
   </si>
   <si>
-    <t>University of Haifa</t>
-  </si>
-  <si>
-    <t>Haifa</t>
-  </si>
-  <si>
-    <t>University of Lincoln</t>
-  </si>
-  <si>
-    <t>Lincoln</t>
-  </si>
-  <si>
-    <t>University of Oregon</t>
-  </si>
-  <si>
-    <t>Eugene, OR</t>
-  </si>
-  <si>
-    <t>University of Trento</t>
-  </si>
-  <si>
-    <t>Trento</t>
-  </si>
-  <si>
-    <t>IITIS, Polish Academy of Sciences</t>
-  </si>
-  <si>
-    <t>Gliwice</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>Michael Mc Gettrick</t>
-  </si>
-  <si>
-    <t>Nanjing University of Aeronautics and Astronautics</t>
-  </si>
-  <si>
-    <t>Nanjing</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>Universidad Rovira i Verguli</t>
-  </si>
-  <si>
-    <t>Tarragona</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>Universite Grenoble Alpes</t>
-  </si>
-  <si>
-    <t>Grenoble</t>
-  </si>
-  <si>
-    <t>University of Cambridge</t>
-  </si>
-  <si>
-    <t>Cambridge</t>
-  </si>
-  <si>
-    <t>University of Gdansk</t>
-  </si>
-  <si>
-    <t>Gdansk</t>
-  </si>
-  <si>
-    <t>Chinese Academy of Sciences</t>
-  </si>
-  <si>
-    <t>Beijing</t>
-  </si>
-  <si>
-    <t>Niall Madden</t>
-  </si>
-  <si>
-    <t>Computational Science Research Center</t>
-  </si>
-  <si>
-    <t>Cooch Behar Panchanan Barma University</t>
-  </si>
-  <si>
-    <t>Cooch Behar</t>
-  </si>
-  <si>
-    <t>DIT University</t>
-  </si>
-  <si>
-    <t>Dehradun</t>
-  </si>
-  <si>
-    <t>Dublin City University</t>
-  </si>
-  <si>
-    <t>Dublin</t>
-  </si>
-  <si>
-    <t>FernUniversitat in Hagen</t>
-  </si>
-  <si>
-    <t>Hagen</t>
-  </si>
-  <si>
-    <t>IIT Trichy</t>
-  </si>
-  <si>
-    <t>Tiruchirappalli</t>
-  </si>
-  <si>
-    <t>Lawrence Berkeley National Laboratory</t>
-  </si>
-  <si>
-    <t>Berkeley</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Maynooth University</t>
-  </si>
-  <si>
-    <t>Kildare</t>
-  </si>
-  <si>
-    <t>Memorial University of Newfoundland</t>
-  </si>
-  <si>
-    <t>St. John’s</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>Santa Clara University</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Technical University of Dublin</t>
-  </si>
-  <si>
-    <t>Trinity College Dublin</t>
-  </si>
-  <si>
-    <t>TU Dresden</t>
-  </si>
-  <si>
-    <t>Dresden</t>
-  </si>
-  <si>
-    <t>TU Wien</t>
-  </si>
-  <si>
-    <t>Vienna</t>
-  </si>
-  <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>Tufts Univerity</t>
-  </si>
-  <si>
-    <t>Medford</t>
-  </si>
-  <si>
-    <t>University College Cork</t>
-  </si>
-  <si>
-    <t>Cork</t>
-  </si>
-  <si>
-    <t>University of Cyprus</t>
-  </si>
-  <si>
-    <t>Nicosia</t>
-  </si>
-  <si>
-    <t>Cyprus</t>
-  </si>
-  <si>
-    <t>University of Limerick</t>
-  </si>
-  <si>
-    <t>Limerick</t>
-  </si>
-  <si>
-    <t>University of Oxford</t>
-  </si>
-  <si>
-    <t>Oxford</t>
-  </si>
-  <si>
-    <t>University of Zaragoza</t>
-  </si>
-  <si>
-    <t>Zaragoza</t>
-  </si>
-  <si>
-    <t>Cardiff University</t>
-  </si>
-  <si>
-    <t>Cardiff</t>
-  </si>
-  <si>
-    <t>Wales</t>
-  </si>
-  <si>
-    <t>Rachel Quinlan</t>
-  </si>
-  <si>
-    <t>Zayed University</t>
-  </si>
-  <si>
-    <t>Dubai</t>
-  </si>
-  <si>
-    <t>United Arab Emirates</t>
-  </si>
-  <si>
-    <t>Abo Adakemi</t>
-  </si>
-  <si>
-    <t>Turku</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>Ray Ryan</t>
-  </si>
-  <si>
     <t>Universidad Torcuato di Tella</t>
   </si>
   <si>
@@ -621,52 +663,31 @@
     <t>Argentina</t>
   </si>
   <si>
-    <t>Universidade Federal do Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>University College Dublin</t>
-  </si>
-  <si>
-    <t>Dane Flannery</t>
-  </si>
-  <si>
-    <t>Universidad de Sevilla</t>
-  </si>
-  <si>
-    <t>Sevilla</t>
-  </si>
-  <si>
-    <t>University of Huddersfield</t>
-  </si>
-  <si>
-    <t>Huddersfield</t>
-  </si>
-  <si>
-    <t>Nina Snigireva</t>
-  </si>
-  <si>
-    <t>Nicolaus Copernicus University in Torun</t>
-  </si>
-  <si>
-    <t>Torun</t>
-  </si>
-  <si>
-    <t>Lodz University of Technology</t>
-  </si>
-  <si>
-    <t>Lodz</t>
-  </si>
-  <si>
-    <t>University of Florida</t>
-  </si>
-  <si>
-    <t>Florida</t>
+    <t>Aalto University</t>
+  </si>
+  <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
+    <t>Emil Sköldberg</t>
+  </si>
+  <si>
+    <t>Uppsala University</t>
+  </si>
+  <si>
+    <t>Uppsala</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City University of Education</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
   </si>
 </sst>
 </file>
@@ -752,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -767,6 +788,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1133,74 +1155,74 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15">
+      <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1208,1081 +1230,1081 @@
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
         <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
         <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15">
       <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
         <v>50</v>
-      </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15">
       <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" t="s">
         <v>66</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>67</v>
       </c>
-      <c r="C26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15">
-      <c r="A27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
       <c r="C27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" t="s">
-        <v>71</v>
+        <v>46</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>71</v>
+        <v>46</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>71</v>
+        <v>82</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" t="s">
-        <v>101</v>
+        <v>97</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="D41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" t="s">
-        <v>124</v>
+        <v>114</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B51" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15">
       <c r="A53" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15">
       <c r="A54" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15">
       <c r="A57" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15">
       <c r="A59" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15">
       <c r="A60" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15">
       <c r="A61" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D61" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C63" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15">
-      <c r="A64" t="s">
-        <v>159</v>
+      <c r="A64" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C64" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
-      </c>
-      <c r="D65" t="s">
-        <v>139</v>
+        <v>151</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15">
       <c r="A66" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="D66" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15">
       <c r="A67" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
-      </c>
-      <c r="D67" t="s">
-        <v>139</v>
+        <v>151</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15">
       <c r="A68" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B68" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D68" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15">
       <c r="A69" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B69" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D69" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15">
       <c r="A70" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
-      </c>
-      <c r="D70" t="s">
-        <v>139</v>
+        <v>151</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15">
       <c r="A71" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B71" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
-      </c>
-      <c r="D71" t="s">
-        <v>139</v>
+        <v>164</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15">
       <c r="A72" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B72" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="D72" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15">
-      <c r="A73" t="s">
-        <v>177</v>
-      </c>
-      <c r="B73" t="s">
-        <v>178</v>
-      </c>
-      <c r="C73" t="s">
-        <v>80</v>
-      </c>
-      <c r="D73" t="s">
-        <v>139</v>
+      <c r="A73" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15">
       <c r="A74" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B74" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15">
       <c r="A75" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B75" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C75" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D75" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="D76" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C77" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15">
-      <c r="A78" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>191</v>
+      <c r="A78" t="s">
+        <v>179</v>
+      </c>
+      <c r="B78" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" t="s">
+        <v>47</v>
       </c>
       <c r="E78" s="4"/>
     </row>
     <row r="79" spans="1:5" ht="15">
       <c r="A79" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C79" t="s">
-        <v>194</v>
-      </c>
-      <c r="D79" t="s">
-        <v>191</v>
+        <v>184</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15">
       <c r="A80" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B80" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C80" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D80" t="s">
-        <v>191</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15">
       <c r="A81" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B81" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="D81" t="s">
-        <v>191</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15">
-      <c r="A82" s="7" t="s">
-        <v>104</v>
+      <c r="A82" t="s">
+        <v>187</v>
       </c>
       <c r="B82" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>184</v>
       </c>
       <c r="D82" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15">
       <c r="A83" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C83" t="s">
-        <v>130</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>199</v>
+        <v>191</v>
+      </c>
+      <c r="D83" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>80</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>199</v>
+        <v>194</v>
+      </c>
+      <c r="D84" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
+      </c>
+      <c r="D85" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15">
@@ -2290,55 +2312,97 @@
         <v>198</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>199</v>
       </c>
       <c r="C86" t="s">
-        <v>85</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
+      </c>
+      <c r="D86" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15">
       <c r="A87" t="s">
+        <v>201</v>
+      </c>
+      <c r="B87" t="s">
+        <v>202</v>
+      </c>
+      <c r="C87" t="s">
+        <v>203</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15">
+      <c r="A88" t="s">
+        <v>204</v>
+      </c>
+      <c r="B88" t="s">
         <v>205</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C88" t="s">
+        <v>203</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15">
+      <c r="A89" t="s">
         <v>206</v>
       </c>
-      <c r="C87" t="s">
-        <v>123</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
+      <c r="B89" t="s">
         <v>207</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C89" t="s">
         <v>208</v>
       </c>
-      <c r="C88" t="s">
-        <v>123</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
+      <c r="D89" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15">
+      <c r="A90" t="s">
         <v>209</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>210</v>
       </c>
-      <c r="C89" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>204</v>
+      <c r="C90" t="s">
+        <v>169</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15">
+      <c r="A91" t="s">
+        <v>212</v>
+      </c>
+      <c r="B91" t="s">
+        <v>213</v>
+      </c>
+      <c r="C91" t="s">
+        <v>214</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15">
+      <c r="A92" t="s">
+        <v>215</v>
+      </c>
+      <c r="B92" t="s">
+        <v>216</v>
+      </c>
+      <c r="C92" t="s">
+        <v>217</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="97" ht="15"/>
@@ -2362,12 +2426,12 @@
     <row r="115" ht="15"/>
     <row r="137" ht="15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H81">
-    <sortCondition ref="D2:D81"/>
-    <sortCondition ref="A2:A81"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D89">
+    <sortCondition descending="1" ref="C2:C89"/>
+    <sortCondition ref="B2:B89"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A54" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
+    <hyperlink ref="A75" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
